--- a/Side Bar Files/GWD Data/PVC Fittings.xlsx
+++ b/Side Bar Files/GWD Data/PVC Fittings.xlsx
@@ -470,12 +470,18 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -950,7 +956,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB1937EB-4448-43ED-A1F9-AAEFD97FB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F6212D-BDF2-4CB3-A6B5-4E8FAF0EB9A7}">
   <dimension ref="A1:G208"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC Fittings.xlsx
+++ b/Side Bar Files/GWD Data/PVC Fittings.xlsx
@@ -9,13 +9,19 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+  </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="60">
   <si>
     <t>Sor/Spec Code</t>
   </si>
@@ -262,6 +268,15 @@
   <si>
     <t>PVC Coupling 280mm, 8 kg/cm2</t>
   </si>
+  <si>
+    <t>Providing and fixing PVC moulded fittings / accessories for Rigid PVC pipes, including jointing with PVC solvent cement - 140 mm dia Elbow</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>PVC Elbow 140 mm dia</t>
+  </si>
 </sst>
 </file>
 
@@ -270,7 +285,7 @@
   <numFmts count="1">
     <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -278,8 +293,35 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF212529"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF212529"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
       <family val="2"/>
     </font>
@@ -293,20 +335,6 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF212529"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
       <family val="2"/>
     </font>
@@ -437,32 +465,18 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -470,16 +484,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -488,98 +502,152 @@
     <xf numFmtId="2" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -658,6 +726,113 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="GWD DR Abstract"/>
+      <sheetName val="GWD MR Abstract"/>
+      <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="ARS Filter Media"/>
+      <sheetName val="BW Casing Pipes"/>
+      <sheetName val="Electrical Essentials"/>
+      <sheetName val="GI on Wall PRICE"/>
+      <sheetName val="GI wo Trench"/>
+      <sheetName val="GI With Trench PRICE"/>
+      <sheetName val="GI Works"/>
+      <sheetName val="Gravel for TWC"/>
+      <sheetName val="Gutter&amp;Clamp"/>
+      <sheetName val="HP Erection and Pullout"/>
+      <sheetName val="HP Repair Labour"/>
+      <sheetName val="HP Repair Spares"/>
+      <sheetName val="Hydrants"/>
+      <sheetName val="Iron Structure"/>
+      <sheetName val="Lock"/>
+      <sheetName val="Metallic PH"/>
+      <sheetName val="Motor Starter GWD"/>
+      <sheetName val="Motor Starter Monoblock"/>
+      <sheetName val="Motor Starter PRICE"/>
+      <sheetName val="Other Fittings PRICE"/>
+      <sheetName val="Panel Board"/>
+      <sheetName val="Pump Cover"/>
+      <sheetName val="Pump Erection "/>
+      <sheetName val="Pump Pullout"/>
+      <sheetName val="PVC Fittings"/>
+      <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall (Concealed) PRICE"/>
+      <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
+      <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
+      <sheetName val="PVC With Trench"/>
+      <sheetName val="Scaffolding"/>
+      <sheetName val="Services"/>
+      <sheetName val="TW Casing Pipes"/>
+      <sheetName val="UG Cable PRICE"/>
+      <sheetName val="Water Meter"/>
+      <sheetName val="Water Tank"/>
+      <sheetName val="Well Protection"/>
+      <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
+      <sheetName val="ZCost Index"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -956,8 +1131,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F6212D-BDF2-4CB3-A6B5-4E8FAF0EB9A7}">
-  <dimension ref="A1:G208"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF3CD8F-D3C9-4929-B048-1F7494E5BAA6}">
+  <dimension ref="A1:G234"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:7" ht="12.75">
@@ -1471,6 +1646,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="21">
+        <f t="array" ref="E34">IFERROR(INDEX(LMRRates,MATCH(B33,LMRCodes,0),),)</f>
         <v>52</v>
       </c>
       <c r="F34" s="35">
@@ -1868,7 +2044,8 @@
       <c r="D60" s="21">
         <v>1</v>
       </c>
-      <c r="E60" s="35">
+      <c r="E60" s="21">
+        <f t="array" ref="E60">IFERROR(INDEX(LMRRates,MATCH(B59,LMRCodes,0),),)</f>
         <v>160</v>
       </c>
       <c r="F60" s="35">
@@ -2267,6 +2444,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="21">
+        <f t="array" ref="E86">IFERROR(INDEX(LMRRates,MATCH(B85,LMRCodes,0),),)</f>
         <v>185</v>
       </c>
       <c r="F86" s="35">
@@ -2665,6 +2843,7 @@
         <v>1</v>
       </c>
       <c r="E112" s="21">
+        <f t="array" ref="E112">IFERROR(INDEX(LMRRates,MATCH(B111,LMRCodes,0),),)</f>
         <v>211</v>
       </c>
       <c r="F112" s="35">
@@ -3063,6 +3242,7 @@
         <v>1</v>
       </c>
       <c r="E138" s="21">
+        <f t="array" ref="E138">IFERROR(INDEX(LMRRates,MATCH(B137,LMRCodes,0),),)</f>
         <v>340</v>
       </c>
       <c r="F138" s="35">
@@ -3461,6 +3641,7 @@
         <v>1</v>
       </c>
       <c r="E164" s="21">
+        <f t="array" ref="E164">IFERROR(INDEX(LMRRates,MATCH(B163,LMRCodes,0),),)</f>
         <v>893</v>
       </c>
       <c r="F164" s="35">
@@ -3859,6 +4040,7 @@
         <v>1</v>
       </c>
       <c r="E190" s="21">
+        <f t="array" ref="E190">IFERROR(INDEX(LMRRates,MATCH(B189,LMRCodes,0),),)</f>
         <v>1000</v>
       </c>
       <c r="F190" s="35">
@@ -4144,8 +4326,406 @@
       <c r="F208" s="3"/>
       <c r="G208" s="4"/>
     </row>
+    <row r="209" spans="1:7" ht="12.75">
+      <c r="A209" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B209" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C209" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D209" s="3"/>
+      <c r="E209" s="4"/>
+      <c r="F209" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="G209" s="4"/>
+    </row>
+    <row r="210" spans="1:7" ht="12.75">
+      <c r="A210" s="6"/>
+      <c r="B210" s="6"/>
+      <c r="C210" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="D210" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="E210" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="F210" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G210" s="39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="12.75">
+      <c r="A211" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B211" s="3"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
+      <c r="E211" s="3"/>
+      <c r="F211" s="3"/>
+      <c r="G211" s="4"/>
+    </row>
+    <row r="212" spans="1:7" ht="12.75">
+      <c r="A212" s="41"/>
+      <c r="B212" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C212" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D212" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E212" s="43">
+        <v>1</v>
+      </c>
+      <c r="F212" s="44"/>
+      <c r="G212" s="4"/>
+    </row>
+    <row r="213" spans="1:7" ht="12.75">
+      <c r="A213" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B213" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
+      <c r="E213" s="3"/>
+      <c r="F213" s="3"/>
+      <c r="G213" s="4"/>
+    </row>
+    <row r="214" spans="1:7" ht="12.75">
+      <c r="A214" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
+      <c r="E214" s="3"/>
+      <c r="F214" s="4"/>
+      <c r="G214" s="47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="12.75">
+      <c r="A215" s="48"/>
+      <c r="B215" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C215" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="D215" s="3"/>
+      <c r="E215" s="4"/>
+      <c r="F215" s="44"/>
+      <c r="G215" s="4"/>
+    </row>
+    <row r="216" spans="1:7" ht="12.75">
+      <c r="A216" s="6"/>
+      <c r="B216" s="6"/>
+      <c r="C216" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D216" s="43">
+        <v>1</v>
+      </c>
+      <c r="E216" s="43">
+        <v>62</v>
+      </c>
+      <c r="F216" s="43">
+        <f>D216*E216</f>
+        <v>62</v>
+      </c>
+      <c r="G216" s="42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" ht="12.75">
+      <c r="A217" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B217" s="3"/>
+      <c r="C217" s="4"/>
+      <c r="D217" s="43">
+        <v>1</v>
+      </c>
+      <c r="E217" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F217" s="43">
+        <f>F216</f>
+        <v>62</v>
+      </c>
+      <c r="G217" s="41"/>
+    </row>
+    <row r="218" spans="1:7" ht="12.75">
+      <c r="A218" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B218" s="3"/>
+      <c r="C218" s="4"/>
+      <c r="D218" s="43">
+        <v>1</v>
+      </c>
+      <c r="E218" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F218" s="43">
+        <f>F217/D217</f>
+        <v>62</v>
+      </c>
+      <c r="G218" s="41"/>
+    </row>
+    <row r="219" spans="1:7" ht="12.75">
+      <c r="A219" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B219" s="3"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="4"/>
+      <c r="E219" s="41"/>
+      <c r="F219" s="43">
+        <f>F218*1%</f>
+        <v>0.62</v>
+      </c>
+      <c r="G219" s="41"/>
+    </row>
+    <row r="220" spans="1:7" ht="12.75">
+      <c r="A220" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B220" s="3"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="4"/>
+      <c r="E220" s="41"/>
+      <c r="F220" s="43">
+        <f>F219+F218</f>
+        <v>62.62</v>
+      </c>
+      <c r="G220" s="41"/>
+    </row>
+    <row r="221" spans="1:7" ht="12.75">
+      <c r="A221" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="4"/>
+      <c r="E221" s="41"/>
+      <c r="F221" s="43">
+        <f>F220*15%</f>
+        <v>9.3930000000000007</v>
+      </c>
+      <c r="G221" s="41"/>
+    </row>
+    <row r="222" spans="1:7" ht="12.75">
+      <c r="A222" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B222" s="3"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="4"/>
+      <c r="E222" s="41"/>
+      <c r="F222" s="52">
+        <f>ROUND(F221+F220,2)</f>
+        <v>72.01</v>
+      </c>
+      <c r="G222" s="41"/>
+    </row>
+    <row r="223" spans="1:7" ht="12.75">
+      <c r="A223" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B223" s="3"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3"/>
+      <c r="E223" s="3"/>
+      <c r="F223" s="4"/>
+      <c r="G223" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="12.75">
+      <c r="A224" s="53">
+        <v>9999</v>
+      </c>
+      <c r="B224" s="48"/>
+      <c r="C224" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D224" s="3"/>
+      <c r="E224" s="4"/>
+      <c r="F224" s="44"/>
+      <c r="G224" s="4"/>
+    </row>
+    <row r="225" spans="1:7" ht="12.75">
+      <c r="A225" s="6"/>
+      <c r="B225" s="6"/>
+      <c r="C225" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="D225" s="43">
+        <v>2.73</v>
+      </c>
+      <c r="E225" s="43">
+        <v>2.12</v>
+      </c>
+      <c r="F225" s="43">
+        <f>E225*D225</f>
+        <v>5.7876000000000003</v>
+      </c>
+      <c r="G225" s="42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="12.75">
+      <c r="A226" s="53">
+        <v>9999</v>
+      </c>
+      <c r="B226" s="48"/>
+      <c r="C226" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D226" s="3"/>
+      <c r="E226" s="4"/>
+      <c r="F226" s="44"/>
+      <c r="G226" s="4"/>
+    </row>
+    <row r="227" spans="1:7" ht="12.75">
+      <c r="A227" s="6"/>
+      <c r="B227" s="6"/>
+      <c r="C227" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="D227" s="43">
+        <v>10.79</v>
+      </c>
+      <c r="E227" s="43">
+        <v>2.12</v>
+      </c>
+      <c r="F227" s="43">
+        <f>D227*E227</f>
+        <v>22.8748</v>
+      </c>
+      <c r="G227" s="42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="12.75">
+      <c r="A228" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B228" s="3"/>
+      <c r="C228" s="4"/>
+      <c r="D228" s="43">
+        <v>1</v>
+      </c>
+      <c r="E228" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F228" s="43">
+        <f>F227+F225</f>
+        <v>28.662400000000002</v>
+      </c>
+      <c r="G228" s="41"/>
+    </row>
+    <row r="229" spans="1:7" ht="12.75">
+      <c r="A229" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B229" s="3"/>
+      <c r="C229" s="4"/>
+      <c r="D229" s="43">
+        <v>1</v>
+      </c>
+      <c r="E229" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F229" s="43">
+        <f>F228/D228</f>
+        <v>28.662400000000002</v>
+      </c>
+      <c r="G229" s="41"/>
+    </row>
+    <row r="230" spans="1:7" ht="12.75">
+      <c r="A230" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B230" s="3"/>
+      <c r="C230" s="3"/>
+      <c r="D230" s="4"/>
+      <c r="E230" s="41"/>
+      <c r="F230" s="43">
+        <f>F229*1%</f>
+        <v>0.28662399999999999</v>
+      </c>
+      <c r="G230" s="41"/>
+    </row>
+    <row r="231" spans="1:7" ht="12.75">
+      <c r="A231" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B231" s="3"/>
+      <c r="C231" s="3"/>
+      <c r="D231" s="4"/>
+      <c r="E231" s="41"/>
+      <c r="F231" s="43">
+        <f>F230+F229</f>
+        <v>28.949024000000001</v>
+      </c>
+      <c r="G231" s="41"/>
+    </row>
+    <row r="232" spans="1:7" ht="12.75">
+      <c r="A232" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B232" s="3"/>
+      <c r="C232" s="3"/>
+      <c r="D232" s="4"/>
+      <c r="E232" s="41"/>
+      <c r="F232" s="43">
+        <f>F231*15%</f>
+        <v>4.3423536</v>
+      </c>
+      <c r="G232" s="41"/>
+    </row>
+    <row r="233" spans="1:7" ht="12.75">
+      <c r="A233" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B233" s="3"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="4"/>
+      <c r="E233" s="41"/>
+      <c r="F233" s="52">
+        <f>ROUND(F232+F231,2)</f>
+        <v>33.29</v>
+      </c>
+      <c r="G233" s="41"/>
+    </row>
+    <row r="234" spans="1:7" ht="12.75">
+      <c r="A234" s="54" t="str">
+        <f>CONCATENATE("Say ₹ ",F222," + ",F233," x Cost Index")</f>
+        <v>Say ₹ 72.01 + 33.29 x Cost Index</v>
+      </c>
+      <c r="B234" s="3"/>
+      <c r="C234" s="3"/>
+      <c r="D234" s="3"/>
+      <c r="E234" s="3"/>
+      <c r="F234" s="3"/>
+      <c r="G234" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="272">
+  <mergeCells count="306">
     <mergeCell ref="F157:G157"/>
     <mergeCell ref="A159:G159"/>
     <mergeCell ref="F160:G160"/>
@@ -4160,44 +4740,6 @@
     <mergeCell ref="A169:D169"/>
     <mergeCell ref="A170:D170"/>
     <mergeCell ref="A171:F171"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="A180:D180"/>
-    <mergeCell ref="A181:D181"/>
-    <mergeCell ref="A182:G182"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="B183:B184"/>
-    <mergeCell ref="F183:G183"/>
-    <mergeCell ref="C189:E189"/>
-    <mergeCell ref="F189:G189"/>
-    <mergeCell ref="C183:E183"/>
-    <mergeCell ref="A185:G185"/>
-    <mergeCell ref="F186:G186"/>
-    <mergeCell ref="B187:G187"/>
-    <mergeCell ref="A188:F188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="B189:B190"/>
-    <mergeCell ref="C198:E198"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="C200:E200"/>
-    <mergeCell ref="F200:G200"/>
-    <mergeCell ref="A191:C191"/>
-    <mergeCell ref="A192:C192"/>
-    <mergeCell ref="A193:D193"/>
-    <mergeCell ref="A194:D194"/>
-    <mergeCell ref="A195:D195"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="A205:D205"/>
-    <mergeCell ref="A206:D206"/>
-    <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A208:G208"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="A202:C202"/>
-    <mergeCell ref="A203:C203"/>
-    <mergeCell ref="A204:D204"/>
     <mergeCell ref="A139:C139"/>
     <mergeCell ref="A140:C140"/>
     <mergeCell ref="A141:D141"/>
@@ -4234,6 +4776,78 @@
     <mergeCell ref="A176:C176"/>
     <mergeCell ref="A177:C177"/>
     <mergeCell ref="A178:D178"/>
+    <mergeCell ref="A205:D205"/>
+    <mergeCell ref="A206:D206"/>
+    <mergeCell ref="A207:D207"/>
+    <mergeCell ref="A208:G208"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="B209:B210"/>
+    <mergeCell ref="F209:G209"/>
+    <mergeCell ref="C209:E209"/>
+    <mergeCell ref="A211:G211"/>
+    <mergeCell ref="F212:G212"/>
+    <mergeCell ref="B213:G213"/>
+    <mergeCell ref="A214:F214"/>
+    <mergeCell ref="A215:A216"/>
+    <mergeCell ref="B215:B216"/>
+    <mergeCell ref="C224:E224"/>
+    <mergeCell ref="F224:G224"/>
+    <mergeCell ref="C226:E226"/>
+    <mergeCell ref="F226:G226"/>
+    <mergeCell ref="A217:C217"/>
+    <mergeCell ref="A218:C218"/>
+    <mergeCell ref="A219:D219"/>
+    <mergeCell ref="A220:D220"/>
+    <mergeCell ref="A221:D221"/>
+    <mergeCell ref="A222:D222"/>
+    <mergeCell ref="A223:F223"/>
+    <mergeCell ref="A231:D231"/>
+    <mergeCell ref="A232:D232"/>
+    <mergeCell ref="A233:D233"/>
+    <mergeCell ref="A234:G234"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="A228:C228"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A230:D230"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="A180:D180"/>
+    <mergeCell ref="A181:D181"/>
+    <mergeCell ref="A182:G182"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="B183:B184"/>
+    <mergeCell ref="F183:G183"/>
+    <mergeCell ref="C189:E189"/>
+    <mergeCell ref="F189:G189"/>
+    <mergeCell ref="C183:E183"/>
+    <mergeCell ref="A185:G185"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="B187:G187"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="B189:B190"/>
+    <mergeCell ref="C198:E198"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="C200:E200"/>
+    <mergeCell ref="F200:G200"/>
+    <mergeCell ref="A191:C191"/>
+    <mergeCell ref="A192:C192"/>
+    <mergeCell ref="A193:D193"/>
+    <mergeCell ref="A194:D194"/>
+    <mergeCell ref="A195:D195"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="A200:A201"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="A202:C202"/>
+    <mergeCell ref="A203:C203"/>
+    <mergeCell ref="A204:D204"/>
+    <mergeCell ref="C215:E215"/>
+    <mergeCell ref="F215:G215"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A25:D25"/>

--- a/Side Bar Files/GWD Data/PVC Fittings.xlsx
+++ b/Side Bar Files/GWD Data/PVC Fittings.xlsx
@@ -1131,7 +1131,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF3CD8F-D3C9-4929-B048-1F7494E5BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED70BD8-A895-4EBE-B0E8-FC3DAEADBAA6}">
   <dimension ref="A1:G234"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC Fittings.xlsx
+++ b/Side Bar Files/GWD Data/PVC Fittings.xlsx
@@ -13,8 +13,8 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
-    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+    <definedName name="LMRRates">[1]zLMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]zLMR!$A:$A</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -776,10 +776,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -1131,7 +1131,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED70BD8-A895-4EBE-B0E8-FC3DAEADBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939044C7-5950-4AFD-B542-CCB6D394BAA6}">
   <dimension ref="A1:G234"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
